--- a/artfynd/A 34173-2026 artfynd.xlsx
+++ b/artfynd/A 34173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136466213</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136468418</v>
       </c>
       <c r="B3" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136466874</v>
       </c>
       <c r="B4" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>136462746</v>
       </c>
       <c r="B41" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>136468195</v>
       </c>
       <c r="B42" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34173-2026 artfynd.xlsx
+++ b/artfynd/A 34173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136466213</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136468418</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136466874</v>
       </c>
       <c r="B4" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>136462746</v>
       </c>
       <c r="B41" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>136468195</v>
       </c>
       <c r="B42" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34173-2026 artfynd.xlsx
+++ b/artfynd/A 34173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136466213</v>
       </c>
       <c r="B2" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136468418</v>
       </c>
       <c r="B3" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136466874</v>
       </c>
       <c r="B4" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136468597</v>
       </c>
       <c r="B5" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136461653</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136461877</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136462469</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136462773</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136463288</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136464161</v>
       </c>
       <c r="B12" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>136464578</v>
       </c>
       <c r="B13" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136466422</v>
       </c>
       <c r="B14" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136468534</v>
       </c>
       <c r="B15" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>136468611</v>
       </c>
       <c r="B16" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136470204</v>
       </c>
       <c r="B17" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136471654</v>
       </c>
       <c r="B18" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>136471766</v>
       </c>
       <c r="B19" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136472000</v>
       </c>
       <c r="B20" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136465301</v>
       </c>
       <c r="B21" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>136468829</v>
       </c>
       <c r="B22" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>136462766</v>
       </c>
       <c r="B26" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>136466133</v>
       </c>
       <c r="B27" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136468785</v>
       </c>
       <c r="B28" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>136469978</v>
       </c>
       <c r="B29" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136471638</v>
       </c>
       <c r="B30" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>136471839</v>
       </c>
       <c r="B31" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>136471891</v>
       </c>
       <c r="B32" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>136471942</v>
       </c>
       <c r="B33" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>136471956</v>
       </c>
       <c r="B34" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136471978</v>
       </c>
       <c r="B35" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>136471996</v>
       </c>
       <c r="B36" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136461813</v>
       </c>
       <c r="B38" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136465043</v>
       </c>
       <c r="B39" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>136462746</v>
       </c>
       <c r="B41" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>136468195</v>
       </c>
       <c r="B42" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136471742</v>
       </c>
       <c r="B43" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 34173-2026 artfynd.xlsx
+++ b/artfynd/A 34173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136466213</v>
       </c>
       <c r="B2" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136468418</v>
       </c>
       <c r="B3" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136466874</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>136462746</v>
       </c>
       <c r="B41" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>136468195</v>
       </c>
       <c r="B42" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34173-2026 artfynd.xlsx
+++ b/artfynd/A 34173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136466213</v>
       </c>
       <c r="B2" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136468418</v>
       </c>
       <c r="B3" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136466874</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136468597</v>
       </c>
       <c r="B5" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136461653</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136461877</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136462469</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136462773</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136463288</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136464161</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>136464578</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136466422</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136468534</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>136468611</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136470204</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136471654</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>136471766</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136472000</v>
       </c>
       <c r="B20" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136465301</v>
       </c>
       <c r="B21" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>136468829</v>
       </c>
       <c r="B22" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>136462746</v>
       </c>
       <c r="B41" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>136468195</v>
       </c>
       <c r="B42" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136471742</v>
       </c>
       <c r="B43" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 34173-2026 artfynd.xlsx
+++ b/artfynd/A 34173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136466213</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136468418</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136466874</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136468597</v>
       </c>
       <c r="B5" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136461653</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136461877</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136462469</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136462773</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136463288</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136464161</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>136464578</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136466422</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136468534</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>136468611</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136470204</v>
       </c>
       <c r="B17" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136471654</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>136471766</v>
       </c>
       <c r="B19" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136472000</v>
       </c>
       <c r="B20" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136465301</v>
       </c>
       <c r="B21" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>136468829</v>
       </c>
       <c r="B22" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>136462746</v>
       </c>
       <c r="B41" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>136468195</v>
       </c>
       <c r="B42" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136471742</v>
       </c>
       <c r="B43" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 34173-2026 artfynd.xlsx
+++ b/artfynd/A 34173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136466213</v>
       </c>
       <c r="B2" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136468418</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136466874</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136468597</v>
       </c>
       <c r="B5" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136461653</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136461877</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136462469</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136462773</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136463288</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136464161</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>136464578</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136466422</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136468534</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>136468611</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136470204</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136471654</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>136471766</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136472000</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136465301</v>
       </c>
       <c r="B21" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>136468829</v>
       </c>
       <c r="B22" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>136462746</v>
       </c>
       <c r="B41" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>136468195</v>
       </c>
       <c r="B42" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136471742</v>
       </c>
       <c r="B43" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 34173-2026 artfynd.xlsx
+++ b/artfynd/A 34173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136466213</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136468418</v>
       </c>
       <c r="B3" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136466874</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>136462746</v>
       </c>
       <c r="B41" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>136468195</v>
       </c>
       <c r="B42" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
